--- a/artfynd/A 18160-2026 artfynd.xlsx
+++ b/artfynd/A 18160-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127906169</v>
+        <v>123316621</v>
       </c>
       <c r="B2" t="n">
-        <v>56620</v>
+        <v>107690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100053</v>
+        <v>872</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindvalls backe, 434 46 Kungsbacka, Hl</t>
+          <t>Karsmossen, S om, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326434</v>
+        <v>326403</v>
       </c>
       <c r="R2" t="n">
-        <v>6374135</v>
+        <v>6374148</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,21 +758,148 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>David Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>David Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127906168</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lindvalls backe, 434 46 Kungsbacka, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>326434</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6374135</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hanhals</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>

--- a/artfynd/A 18160-2026 artfynd.xlsx
+++ b/artfynd/A 18160-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316621</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127906168</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>